--- a/data/sales_data.xlsx
+++ b/data/sales_data.xlsx
@@ -78,11 +78,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="m/d/yyyy;@"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -691,7 +692,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1230,11 +1231,11 @@
   <dimension ref="A1:E50"/>
   <sheetFormatPr defaultColWidth="8.4375" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.625"/>
+    <col min="1" max="1" width="9.625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">

--- a/data/sales_data.xlsx
+++ b/data/sales_data.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="15">
   <si>
     <t>日期</t>
   </si>
@@ -1228,7 +1228,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr defaultColWidth="8.4375" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="9.625" style="1"/>
@@ -1389,458 +1389,452 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1">
-        <v>46032</v>
+        <v>46043</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>116</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1">
-        <v>46041</v>
+        <v>46032</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D11">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E11">
-        <v>91</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1">
-        <v>46033</v>
+        <v>46041</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D12">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E12">
-        <v>116</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
       </c>
       <c r="D13">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E13">
-        <v>94</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1">
-        <v>46025</v>
+        <v>46034</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D14">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E14">
-        <v>119</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1">
-        <v>46034</v>
+        <v>46025</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
       </c>
       <c r="D15">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E15">
-        <v>79</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1">
-        <v>46039</v>
+        <v>46034</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D16">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E16">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1">
-        <v>46041</v>
+        <v>46039</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D17">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E17">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1">
-        <v>46043</v>
+        <v>46041</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="E18">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E19">
-        <v>100</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1">
-        <v>46047</v>
+        <v>46031</v>
       </c>
       <c r="B20" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D20">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E20">
-        <v>113</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1">
-        <v>46042</v>
+        <v>46047</v>
       </c>
       <c r="B21" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C21" t="s">
         <v>6</v>
       </c>
       <c r="D21">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="E21">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1">
-        <v>46030</v>
+        <v>46042</v>
       </c>
       <c r="B22" t="s">
         <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E22">
-        <v>77</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D23">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>100</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="1">
-        <v>46038</v>
+        <v>46029</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D24">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="E24">
-        <v>117</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1">
-        <v>46023</v>
+        <v>46038</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="E25">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="1">
-        <v>46044</v>
+        <v>46023</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
       </c>
       <c r="D26">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1">
-        <v>46043</v>
+        <v>46041</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27">
-        <v>31</v>
-      </c>
-      <c r="E27">
-        <v>90</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1">
-        <v>46039</v>
+        <v>46044</v>
       </c>
       <c r="B28" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="E28">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1">
-        <v>46047</v>
+        <v>46043</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D29">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E29">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1">
-        <v>46026</v>
+        <v>46039</v>
       </c>
       <c r="B30" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
       </c>
       <c r="D30">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="E30">
-        <v>83</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1">
-        <v>46034</v>
+        <v>46047</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D31">
         <v>25</v>
       </c>
       <c r="E31">
-        <v>113</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1">
-        <v>46033</v>
+        <v>46026</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D32">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E32">
-        <v>121</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1">
-        <v>46048</v>
+        <v>46034</v>
       </c>
       <c r="B33" t="s">
         <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E33">
-        <v>89</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1">
-        <v>46039</v>
+        <v>46033</v>
       </c>
       <c r="B34" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D34">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E34">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1">
-        <v>46037</v>
+        <v>46048</v>
       </c>
       <c r="B35" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D35">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E35">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1">
-        <v>46036</v>
+        <v>46039</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C36" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D36">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E36">
         <v>114</v>
@@ -1848,75 +1842,75 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1">
-        <v>46039</v>
+        <v>46037</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C37" t="s">
         <v>10</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="E37">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1">
-        <v>46039</v>
+        <v>46036</v>
       </c>
       <c r="B38" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D38">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E38">
-        <v>100</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1">
-        <v>46029</v>
+        <v>46040</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C39" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39">
         <v>8</v>
       </c>
-      <c r="D39">
-        <v>19</v>
-      </c>
       <c r="E39">
-        <v>115</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1">
-        <v>46043</v>
+        <v>46039</v>
       </c>
       <c r="B40" t="s">
         <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D40">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>86</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1">
-        <v>46027</v>
+        <v>46039</v>
       </c>
       <c r="B41" t="s">
         <v>7</v>
@@ -1925,15 +1919,15 @@
         <v>6</v>
       </c>
       <c r="D41">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E41">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
@@ -1942,32 +1936,32 @@
         <v>8</v>
       </c>
       <c r="D42">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E42">
-        <v>97</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1">
-        <v>46050</v>
+        <v>46043</v>
       </c>
       <c r="B43" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C43" t="s">
         <v>8</v>
       </c>
       <c r="D43">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="E43">
-        <v>104</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1">
-        <v>46040</v>
+        <v>46027</v>
       </c>
       <c r="B44" t="s">
         <v>7</v>
@@ -1976,111 +1970,162 @@
         <v>6</v>
       </c>
       <c r="D44">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E44">
-        <v>99</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1">
-        <v>46043</v>
+        <v>46030</v>
       </c>
       <c r="B45" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D45">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="E45">
-        <v>78</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="1">
-        <v>46028</v>
+        <v>46050</v>
       </c>
       <c r="B46" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C46" t="s">
         <v>8</v>
       </c>
       <c r="D46">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="E46">
-        <v>86</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1">
-        <v>46032</v>
+        <v>46040</v>
       </c>
       <c r="B47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C47" t="s">
         <v>6</v>
       </c>
       <c r="D47">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E47">
-        <v>119</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="1">
-        <v>46049</v>
+        <v>46043</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C48" t="s">
         <v>6</v>
       </c>
       <c r="D48">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E48">
-        <v>96</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="1">
-        <v>46034</v>
+        <v>46028</v>
       </c>
       <c r="B49" t="s">
         <v>11</v>
       </c>
       <c r="C49" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E49">
-        <v>120</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="1">
+        <v>46032</v>
+      </c>
+      <c r="B50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50">
+        <v>30</v>
+      </c>
+      <c r="E50">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51">
+        <v>38</v>
+      </c>
+      <c r="E51">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B52" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52">
+        <v>5</v>
+      </c>
+      <c r="E52">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="1">
         <v>46028</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B53" t="s">
         <v>5</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C53" t="s">
         <v>8</v>
       </c>
-      <c r="D50">
+      <c r="D53">
         <v>16</v>
       </c>
-      <c r="E50">
+      <c r="E53">
         <v>94</v>
       </c>
     </row>

--- a/data/sales_data.xlsx
+++ b/data/sales_data.xlsx
@@ -7,7 +7,8 @@
     <workbookView windowWidth="21720" windowHeight="11660"/>
   </bookViews>
   <sheets>
-    <sheet name="sales_data" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="18">
   <si>
     <t>日期</t>
   </si>
@@ -73,6 +74,15 @@
   <si>
     <t>苏州</t>
   </si>
+  <si>
+    <t>平均销量</t>
+  </si>
+  <si>
+    <t>最高产品销量</t>
+  </si>
+  <si>
+    <t>最低产品销量</t>
+  </si>
 </sst>
 </file>
 
@@ -85,10 +95,17 @@
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="m/d/yyyy;@"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -432,12 +449,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -558,140 +590,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
@@ -1231,11 +1267,11 @@
   <dimension ref="A1:E53"/>
   <sheetFormatPr defaultColWidth="8.4375" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.625" style="1"/>
+    <col min="1" max="1" width="9.625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -1252,7 +1288,7 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="1">
+      <c r="A2" s="3">
         <v>46050</v>
       </c>
       <c r="B2" t="s">
@@ -1269,7 +1305,7 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="1">
+      <c r="A3" s="3">
         <v>46027</v>
       </c>
       <c r="B3" t="s">
@@ -1286,7 +1322,7 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="1">
+      <c r="A4" s="3">
         <v>46042</v>
       </c>
       <c r="B4" t="s">
@@ -1303,7 +1339,7 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="1">
+      <c r="A5" s="3">
         <v>46031</v>
       </c>
       <c r="B5" t="s">
@@ -1320,7 +1356,7 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="1">
+      <c r="A6" s="3">
         <v>46033</v>
       </c>
       <c r="B6" t="s">
@@ -1337,7 +1373,7 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="1">
+      <c r="A7" s="3">
         <v>46026</v>
       </c>
       <c r="B7" t="s">
@@ -1354,7 +1390,7 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="1">
+      <c r="A8" s="3">
         <v>46025</v>
       </c>
       <c r="B8" t="s">
@@ -1371,7 +1407,7 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="1">
+      <c r="A9" s="3">
         <v>46025</v>
       </c>
       <c r="B9" t="s">
@@ -1388,7 +1424,7 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="1">
+      <c r="A10" s="3">
         <v>46043</v>
       </c>
       <c r="B10" t="s">
@@ -1405,7 +1441,7 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="1">
+      <c r="A11" s="3">
         <v>46032</v>
       </c>
       <c r="B11" t="s">
@@ -1422,7 +1458,7 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="1">
+      <c r="A12" s="3">
         <v>46041</v>
       </c>
       <c r="B12" t="s">
@@ -1439,7 +1475,7 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="1">
+      <c r="A13" s="3">
         <v>46033</v>
       </c>
       <c r="B13" t="s">
@@ -1456,7 +1492,7 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="1">
+      <c r="A14" s="3">
         <v>46034</v>
       </c>
       <c r="B14" t="s">
@@ -1473,7 +1509,7 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="1">
+      <c r="A15" s="3">
         <v>46025</v>
       </c>
       <c r="B15" t="s">
@@ -1490,7 +1526,7 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="1">
+      <c r="A16" s="3">
         <v>46034</v>
       </c>
       <c r="B16" t="s">
@@ -1507,7 +1543,7 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="1">
+      <c r="A17" s="3">
         <v>46039</v>
       </c>
       <c r="B17" t="s">
@@ -1524,7 +1560,7 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="1">
+      <c r="A18" s="3">
         <v>46041</v>
       </c>
       <c r="B18" t="s">
@@ -1541,7 +1577,7 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="1">
+      <c r="A19" s="3">
         <v>46043</v>
       </c>
       <c r="B19" t="s">
@@ -1558,7 +1594,7 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="1">
+      <c r="A20" s="3">
         <v>46031</v>
       </c>
       <c r="B20" t="s">
@@ -1575,7 +1611,7 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="1">
+      <c r="A21" s="3">
         <v>46047</v>
       </c>
       <c r="B21" t="s">
@@ -1592,7 +1628,7 @@
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="1">
+      <c r="A22" s="3">
         <v>46042</v>
       </c>
       <c r="B22" t="s">
@@ -1609,7 +1645,7 @@
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="1">
+      <c r="A23" s="3">
         <v>46030</v>
       </c>
       <c r="B23" t="s">
@@ -1626,7 +1662,7 @@
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="1">
+      <c r="A24" s="3">
         <v>46029</v>
       </c>
       <c r="B24" t="s">
@@ -1643,7 +1679,7 @@
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="1">
+      <c r="A25" s="3">
         <v>46038</v>
       </c>
       <c r="B25" t="s">
@@ -1660,7 +1696,7 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="1">
+      <c r="A26" s="3">
         <v>46023</v>
       </c>
       <c r="B26" t="s">
@@ -1677,7 +1713,7 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="1">
+      <c r="A27" s="3">
         <v>46041</v>
       </c>
       <c r="B27" t="s">
@@ -1688,7 +1724,7 @@
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="1">
+      <c r="A28" s="3">
         <v>46044</v>
       </c>
       <c r="B28" t="s">
@@ -1705,7 +1741,7 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="1">
+      <c r="A29" s="3">
         <v>46043</v>
       </c>
       <c r="B29" t="s">
@@ -1722,7 +1758,7 @@
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="1">
+      <c r="A30" s="3">
         <v>46039</v>
       </c>
       <c r="B30" t="s">
@@ -1739,7 +1775,7 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="1">
+      <c r="A31" s="3">
         <v>46047</v>
       </c>
       <c r="B31" t="s">
@@ -1756,7 +1792,7 @@
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="1">
+      <c r="A32" s="3">
         <v>46026</v>
       </c>
       <c r="B32" t="s">
@@ -1773,7 +1809,7 @@
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="1">
+      <c r="A33" s="3">
         <v>46034</v>
       </c>
       <c r="B33" t="s">
@@ -1790,7 +1826,7 @@
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="1">
+      <c r="A34" s="3">
         <v>46033</v>
       </c>
       <c r="B34" t="s">
@@ -1807,7 +1843,7 @@
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="1">
+      <c r="A35" s="3">
         <v>46048</v>
       </c>
       <c r="B35" t="s">
@@ -1824,7 +1860,7 @@
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="1">
+      <c r="A36" s="3">
         <v>46039</v>
       </c>
       <c r="B36" t="s">
@@ -1841,7 +1877,7 @@
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="1">
+      <c r="A37" s="3">
         <v>46037</v>
       </c>
       <c r="B37" t="s">
@@ -1858,7 +1894,7 @@
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="1">
+      <c r="A38" s="3">
         <v>46036</v>
       </c>
       <c r="B38" t="s">
@@ -1875,7 +1911,7 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="1">
+      <c r="A39" s="3">
         <v>46040</v>
       </c>
       <c r="B39" t="s">
@@ -1892,7 +1928,7 @@
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="1">
+      <c r="A40" s="3">
         <v>46039</v>
       </c>
       <c r="B40" t="s">
@@ -1909,7 +1945,7 @@
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="1">
+      <c r="A41" s="3">
         <v>46039</v>
       </c>
       <c r="B41" t="s">
@@ -1926,7 +1962,7 @@
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="1">
+      <c r="A42" s="3">
         <v>46029</v>
       </c>
       <c r="B42" t="s">
@@ -1943,7 +1979,7 @@
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="1">
+      <c r="A43" s="3">
         <v>46043</v>
       </c>
       <c r="B43" t="s">
@@ -1960,7 +1996,7 @@
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="1">
+      <c r="A44" s="3">
         <v>46027</v>
       </c>
       <c r="B44" t="s">
@@ -1977,7 +2013,7 @@
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="1">
+      <c r="A45" s="3">
         <v>46030</v>
       </c>
       <c r="B45" t="s">
@@ -1994,7 +2030,7 @@
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="1">
+      <c r="A46" s="3">
         <v>46050</v>
       </c>
       <c r="B46" t="s">
@@ -2011,7 +2047,7 @@
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="1">
+      <c r="A47" s="3">
         <v>46040</v>
       </c>
       <c r="B47" t="s">
@@ -2028,7 +2064,7 @@
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="1">
+      <c r="A48" s="3">
         <v>46043</v>
       </c>
       <c r="B48" t="s">
@@ -2045,7 +2081,7 @@
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="1">
+      <c r="A49" s="3">
         <v>46028</v>
       </c>
       <c r="B49" t="s">
@@ -2062,7 +2098,7 @@
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="1">
+      <c r="A50" s="3">
         <v>46032</v>
       </c>
       <c r="B50" t="s">
@@ -2079,7 +2115,7 @@
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="1">
+      <c r="A51" s="3">
         <v>46049</v>
       </c>
       <c r="B51" t="s">
@@ -2096,7 +2132,7 @@
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="1">
+      <c r="A52" s="3">
         <v>46034</v>
       </c>
       <c r="B52" t="s">
@@ -2113,7 +2149,7 @@
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="1">
+      <c r="A53" s="3">
         <v>46028</v>
       </c>
       <c r="B53" t="s">
@@ -2127,6 +2163,116 @@
       </c>
       <c r="E53">
         <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2">
+        <v>34</v>
+      </c>
+      <c r="C2" s="2">
+        <v>107</v>
+      </c>
+      <c r="D2" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2">
+        <v>17.3333333333333</v>
+      </c>
+      <c r="C3" s="2">
+        <v>59</v>
+      </c>
+      <c r="D3" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2">
+        <v>25.1111111111111</v>
+      </c>
+      <c r="C4" s="2">
+        <v>121</v>
+      </c>
+      <c r="D4" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2">
+        <v>18.4545454545454</v>
+      </c>
+      <c r="C5" s="2">
+        <v>69</v>
+      </c>
+      <c r="D5" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2">
+        <v>25.25</v>
+      </c>
+      <c r="C6" s="2">
+        <v>84</v>
+      </c>
+      <c r="D6" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2">
+        <v>21.6</v>
+      </c>
+      <c r="C7" s="2">
+        <v>59</v>
+      </c>
+      <c r="D7" s="2">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
